--- a/ig/DM_FINESS_New/ValueSet-vs-tre-r382-modalite-act-de-soin-amm-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-tre-r382-modalite-act-de-soin-amm-all.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>Property</t>
   </si>
@@ -25,12 +25,6 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r382-modalite-act-de-soin-amm?vs</t>
-  </si>
-  <si>
-    <t>Identifier</t>
-  </si>
-  <si>
-    <t>OID:1.2.250.1.213.1.6.1.354</t>
   </si>
   <si>
     <t>Version</t>
@@ -239,7 +233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -330,28 +324,20 @@
       <c r="A11" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
-      </c>
+      <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -370,28 +356,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/ValueSet-vs-tre-r382-modalite-act-de-soin-amm-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-tre-r382-modalite-act-de-soin-amm-all.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250222120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T18:02:28.249+00:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
